--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.48153663404301</v>
+        <v>1.378249703031989</v>
       </c>
       <c r="D2" t="n">
-        <v>8.759133961781256</v>
+        <v>1.423359268789454</v>
       </c>
       <c r="E2" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F2" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.26316702753925</v>
+        <v>6.867764641975127</v>
       </c>
       <c r="D3" t="n">
-        <v>42.83616691464045</v>
+        <v>6.960877123629073</v>
       </c>
       <c r="E3" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F3" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.26902209838934</v>
+        <v>4.106216090988267</v>
       </c>
       <c r="D4" t="n">
-        <v>24.72811071126315</v>
+        <v>4.018317990580261</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F4" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.82964102503388</v>
+        <v>2.734816666568005</v>
       </c>
       <c r="D5" t="n">
-        <v>16.61203475746049</v>
+        <v>2.69945564808733</v>
       </c>
       <c r="E5" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.49151090171651</v>
+        <v>10.47987052152893</v>
       </c>
       <c r="D6" t="n">
-        <v>53.31731318011044</v>
+        <v>8.664063391767947</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F6" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.9402916529034</v>
+        <v>6.977797393596804</v>
       </c>
       <c r="D7" t="n">
-        <v>29.71707399991763</v>
+        <v>4.829024524986615</v>
       </c>
       <c r="E7" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F7" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.89976408380846</v>
+        <v>5.346211663618875</v>
       </c>
       <c r="D8" t="n">
-        <v>24.44890054638357</v>
+        <v>3.97294633878733</v>
       </c>
       <c r="E8" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F8" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.28971459981588</v>
+        <v>7.684578622470081</v>
       </c>
       <c r="D9" t="n">
-        <v>23.11289385876551</v>
+        <v>3.755845252049396</v>
       </c>
       <c r="E9" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F9" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.51409098983117</v>
+        <v>8.371039785847566</v>
       </c>
       <c r="D10" t="n">
-        <v>20.73665698104208</v>
+        <v>3.369706759419338</v>
       </c>
       <c r="E10" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F10" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.7345419407939</v>
+        <v>7.43186306537901</v>
       </c>
       <c r="D11" t="n">
-        <v>15.51997145120906</v>
+        <v>2.521995360821472</v>
       </c>
       <c r="E11" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F11" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.84352566176358</v>
+        <v>2.412072920036581</v>
       </c>
       <c r="D12" t="n">
-        <v>16.51608319564613</v>
+        <v>2.683863519292497</v>
       </c>
       <c r="E12" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F12" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.64034647915709</v>
+        <v>4.004056302863027</v>
       </c>
       <c r="D13" t="n">
-        <v>6.944604069600585</v>
+        <v>1.128498161310095</v>
       </c>
       <c r="E13" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F13" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.65765299650518</v>
+        <v>5.794368611932093</v>
       </c>
       <c r="D14" t="n">
-        <v>9.299228520369653</v>
+        <v>1.511124634560069</v>
       </c>
       <c r="E14" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F14" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.87104423964173</v>
+        <v>5.504044688941782</v>
       </c>
       <c r="D15" t="n">
-        <v>17.9235995662009</v>
+        <v>2.912584929507646</v>
       </c>
       <c r="E15" t="n">
-        <v>15.05128066314836</v>
+        <v>2.445833107761609</v>
       </c>
       <c r="F15" t="n">
-        <v>12.45367832536815</v>
+        <v>2.023722727872324</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
